--- a/research/traditional_assets/database/data/jamaica/jamaica_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.166</v>
+        <v>0.21</v>
       </c>
       <c r="E2">
-        <v>-0.00233</v>
+        <v>-0.0582</v>
       </c>
       <c r="G2">
-        <v>0.01793222854316102</v>
+        <v>0.06302578018995929</v>
       </c>
       <c r="H2">
-        <v>0.01793222854316102</v>
+        <v>0.06302578018995929</v>
       </c>
       <c r="I2">
-        <v>0.1476131585456344</v>
+        <v>0.05013568521031208</v>
       </c>
       <c r="J2">
-        <v>0.119768754010331</v>
+        <v>0.03432112094178351</v>
       </c>
       <c r="K2">
-        <v>4.224</v>
+        <v>2.234</v>
       </c>
       <c r="L2">
-        <v>0.1044768736087064</v>
+        <v>0.05052012663952962</v>
       </c>
       <c r="M2">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="N2">
-        <v>0.01918223119636547</v>
+        <v>0.02849002849002849</v>
       </c>
       <c r="O2">
-        <v>0.2698863636363636</v>
+        <v>0.5819158460161146</v>
       </c>
       <c r="P2">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Q2">
-        <v>0.01918223119636547</v>
+        <v>0.02849002849002849</v>
       </c>
       <c r="R2">
-        <v>0.2698863636363636</v>
+        <v>0.5819158460161146</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>14.549</v>
+        <v>15.93</v>
       </c>
       <c r="V2">
-        <v>0.244809019013966</v>
+        <v>0.3491124260355029</v>
       </c>
       <c r="W2">
-        <v>0.1778947368421052</v>
+        <v>0.08638743455497383</v>
       </c>
       <c r="X2">
-        <v>0.09265172628940602</v>
+        <v>0.146110285184423</v>
       </c>
       <c r="Y2">
-        <v>0.08524301055269923</v>
+        <v>-0.05972285062944915</v>
       </c>
       <c r="Z2">
-        <v>3.994269907132978</v>
+        <v>2.309138381201044</v>
       </c>
       <c r="AA2">
-        <v>0.04851089960085969</v>
+        <v>0.07100428918110503</v>
       </c>
       <c r="AB2">
-        <v>0.09249390343283453</v>
+        <v>0.1457252115223188</v>
       </c>
       <c r="AC2">
-        <v>-0.04392238849249494</v>
+        <v>-0.07463089690735815</v>
       </c>
       <c r="AD2">
-        <v>0.857</v>
+        <v>0.608</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.857</v>
+        <v>0.608</v>
       </c>
       <c r="AG2">
-        <v>-13.692</v>
+        <v>-15.322</v>
       </c>
       <c r="AH2">
-        <v>0.01421533663973991</v>
+        <v>0.01314935767117955</v>
       </c>
       <c r="AI2">
-        <v>0.02487879931488954</v>
+        <v>0.01869158878504673</v>
       </c>
       <c r="AJ2">
-        <v>-0.2993572084481175</v>
+        <v>-0.5055430909330869</v>
       </c>
       <c r="AK2">
-        <v>-0.6881093577243943</v>
+        <v>-0.923123267863598</v>
       </c>
       <c r="AL2">
-        <v>0.142</v>
+        <v>0.019</v>
       </c>
       <c r="AM2">
-        <v>0.142</v>
+        <v>0.019</v>
       </c>
       <c r="AN2">
-        <v>0.1323347745521927</v>
+        <v>0.247557003257329</v>
       </c>
       <c r="AO2">
-        <v>42.0281690140845</v>
+        <v>116.6842105263158</v>
       </c>
       <c r="AP2">
-        <v>-2.114268066707844</v>
+        <v>-6.238599348534201</v>
       </c>
       <c r="AQ2">
-        <v>42.0281690140845</v>
+        <v>116.6842105263158</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>General Accident Insurance Company Jamaica Limited (JMSE:GENAC)</t>
+          <t>Key Insurance Company Limited (JMSE:KEY)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +722,100 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.171</v>
-      </c>
-      <c r="E3">
-        <v>-0.00233</v>
+        <v>0.136</v>
       </c>
       <c r="G3">
-        <v>0.05574912891986063</v>
+        <v>0.1092592592592593</v>
       </c>
       <c r="H3">
-        <v>0.05574912891986063</v>
+        <v>0.1092592592592593</v>
       </c>
       <c r="I3">
-        <v>0.1167247386759582</v>
+        <v>0.1240740740740741</v>
       </c>
       <c r="J3">
-        <v>0.08984362593530187</v>
+        <v>0.08416720814381633</v>
       </c>
       <c r="K3">
-        <v>3.38</v>
+        <v>1.16</v>
       </c>
       <c r="L3">
-        <v>0.1177700348432056</v>
+        <v>0.1074074074074074</v>
       </c>
       <c r="M3">
-        <v>1.14</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.02821782178217822</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.3372781065088757</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>1.14</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.02821782178217822</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.3372781065088757</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>6.29</v>
+        <v>7.53</v>
       </c>
       <c r="V3">
-        <v>0.1556930693069307</v>
+        <v>0.6172131147540985</v>
       </c>
       <c r="W3">
-        <v>0.1778947368421052</v>
+        <v>0.1792890262751159</v>
       </c>
       <c r="X3">
-        <v>0.09350268134024507</v>
+        <v>0.146110285184423</v>
       </c>
       <c r="Y3">
-        <v>0.08439205550186017</v>
-      </c>
-      <c r="Z3">
-        <v>2.378978779840849</v>
-      </c>
-      <c r="AA3">
-        <v>0.2137360796040421</v>
+        <v>0.03317874109069294</v>
       </c>
       <c r="AB3">
-        <v>0.09283734463565628</v>
-      </c>
-      <c r="AC3">
-        <v>0.1208987349683858</v>
+        <v>0.1457252115223188</v>
       </c>
       <c r="AD3">
-        <v>0.78</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.78</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AG3">
-        <v>-5.51</v>
+        <v>-7.443000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.01894123360854784</v>
+        <v>0.00708065435012615</v>
       </c>
       <c r="AI3">
-        <v>0.03239202657807309</v>
+        <v>0.01225870085951811</v>
       </c>
       <c r="AJ3">
-        <v>-0.1579249068501003</v>
+        <v>-1.564641580828254</v>
       </c>
       <c r="AK3">
-        <v>-0.3097245643620011</v>
+        <v>17.18937644341799</v>
       </c>
       <c r="AL3">
-        <v>0.131</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.131</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.208</v>
-      </c>
-      <c r="AO3">
-        <v>25.57251908396946</v>
+        <v>0.06214285714285715</v>
       </c>
       <c r="AP3">
-        <v>-1.469333333333333</v>
-      </c>
-      <c r="AQ3">
-        <v>25.57251908396946</v>
+        <v>-5.316428571428572</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ironrock Insurance Company Limited (JMSE:ROC)</t>
+          <t>IronRock Insurance Company Limited (JMSE:ROC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,23 +834,26 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.308</v>
+      </c>
       <c r="G4">
-        <v>0.07195571955719557</v>
+        <v>0.09143835616438357</v>
       </c>
       <c r="H4">
-        <v>0.07195571955719557</v>
+        <v>0.09143835616438357</v>
       </c>
       <c r="I4">
-        <v>0.05830258302583026</v>
+        <v>0.1044520547945205</v>
       </c>
       <c r="J4">
-        <v>0.05830258302583026</v>
+        <v>0.09143018058936811</v>
       </c>
       <c r="K4">
-        <v>0.356</v>
+        <v>0.33</v>
       </c>
       <c r="L4">
-        <v>0.1313653136531365</v>
+        <v>0.113013698630137</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -895,73 +877,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.06900000000000001</v>
+        <v>1.16</v>
       </c>
       <c r="V4">
-        <v>0.01593533487297922</v>
+        <v>0.3483483483483483</v>
       </c>
       <c r="W4">
-        <v>0.1008498583569405</v>
+        <v>0.08638743455497383</v>
       </c>
       <c r="X4">
-        <v>0.09250407625847026</v>
+        <v>0.1458038488240062</v>
       </c>
       <c r="Y4">
-        <v>0.008345782098470242</v>
+        <v>-0.05941641426903241</v>
       </c>
       <c r="Z4">
-        <v>0.8320540374577833</v>
+        <v>0.7765957446808511</v>
       </c>
       <c r="AA4">
-        <v>0.04851089960085969</v>
+        <v>0.07100428918110503</v>
       </c>
       <c r="AB4">
-        <v>0.09243328809335463</v>
+        <v>0.1456351860884632</v>
       </c>
       <c r="AC4">
-        <v>-0.04392238849249494</v>
+        <v>-0.07463089690735815</v>
       </c>
       <c r="AD4">
-        <v>0.008999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.008999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="AG4">
-        <v>-0.06</v>
+        <v>-1.149</v>
       </c>
       <c r="AH4">
-        <v>0.002074210647614658</v>
+        <v>0.003292427416941035</v>
       </c>
       <c r="AI4">
-        <v>0.002350483154870723</v>
+        <v>0.002735637901019647</v>
       </c>
       <c r="AJ4">
-        <v>-0.01405152224824356</v>
+        <v>-0.5268225584594223</v>
       </c>
       <c r="AK4">
-        <v>-0.01595744680851064</v>
+        <v>-0.4016078294302692</v>
       </c>
       <c r="AL4">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AM4">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AN4">
-        <v>0.04838709677419355</v>
+        <v>0.03206997084548104</v>
       </c>
       <c r="AO4">
-        <v>14.36363636363637</v>
+        <v>25.41666666666666</v>
       </c>
       <c r="AP4">
-        <v>-0.3225806451612904</v>
+        <v>-3.349854227405248</v>
       </c>
       <c r="AQ4">
-        <v>14.36363636363637</v>
+        <v>25.41666666666666</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Key Insurance Company Limited (JMSE:KEY)</t>
+          <t>General Accident Insurance Company Jamaica Limited (JMSE:GENAC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,109 +963,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.161</v>
+        <v>0.21</v>
+      </c>
+      <c r="E5">
+        <v>-0.0582</v>
       </c>
       <c r="G5">
-        <v>-0.1186252771618625</v>
+        <v>0.0439344262295082</v>
       </c>
       <c r="H5">
-        <v>-0.1186252771618625</v>
+        <v>0.0439344262295082</v>
       </c>
       <c r="I5">
-        <v>0.2727272727272728</v>
+        <v>0.01875409836065573</v>
       </c>
       <c r="J5">
-        <v>0.1812005928853755</v>
+        <v>0.009377049180327867</v>
       </c>
       <c r="K5">
-        <v>0.488</v>
+        <v>0.744</v>
       </c>
       <c r="L5">
-        <v>0.0541019955654102</v>
+        <v>0.02439344262295082</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>1.3</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.04318936877076412</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>1.747311827956989</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>1.3</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.04318936877076412</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>1.747311827956989</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>8.19</v>
+        <v>7.24</v>
       </c>
       <c r="V5">
-        <v>0.5571428571428572</v>
+        <v>0.240531561461794</v>
       </c>
       <c r="W5">
-        <v>0.3753846153846154</v>
+        <v>0.03559808612440191</v>
       </c>
       <c r="X5">
-        <v>0.09265172628940602</v>
+        <v>0.1468958104057642</v>
       </c>
       <c r="Y5">
-        <v>0.2827328890952093</v>
+        <v>-0.1112977242813623</v>
       </c>
       <c r="Z5">
-        <v>-1.734949028659358</v>
+        <v>1.98180636777128</v>
       </c>
       <c r="AA5">
-        <v>-0.3143737926189819</v>
+        <v>0.01858349577647823</v>
       </c>
       <c r="AB5">
-        <v>0.09249390343283453</v>
+        <v>0.1458804016677022</v>
       </c>
       <c r="AC5">
-        <v>-0.4068676960518164</v>
+        <v>-0.127296905891224</v>
       </c>
       <c r="AD5">
-        <v>0.068</v>
+        <v>0.51</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.068</v>
+        <v>0.51</v>
       </c>
       <c r="AG5">
-        <v>-8.122</v>
+        <v>-6.73</v>
       </c>
       <c r="AH5">
-        <v>0.004604550379198267</v>
+        <v>0.01666122182293368</v>
       </c>
       <c r="AI5">
-        <v>0.01040073416947079</v>
+        <v>0.02382064455861747</v>
       </c>
       <c r="AJ5">
-        <v>-1.234721799939191</v>
+        <v>-0.2879760376551134</v>
       </c>
       <c r="AK5">
-        <v>4.916464891041162</v>
+        <v>-0.4749470712773466</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="AN5">
-        <v>0.02677165354330709</v>
+        <v>0.7152875175315568</v>
+      </c>
+      <c r="AO5">
+        <v>81.71428571428571</v>
       </c>
       <c r="AP5">
-        <v>-3.197637795275591</v>
+        <v>-9.438990182328192</v>
+      </c>
+      <c r="AQ5">
+        <v>81.71428571428571</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jamaica/jamaica_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.21</v>
+        <v>0.194</v>
       </c>
       <c r="E2">
-        <v>-0.0582</v>
+        <v>0.359</v>
       </c>
       <c r="G2">
-        <v>0.06302578018995929</v>
+        <v>0.08784955028618152</v>
       </c>
       <c r="H2">
-        <v>0.06302578018995929</v>
+        <v>0.08784955028618152</v>
       </c>
       <c r="I2">
-        <v>0.05013568521031208</v>
+        <v>0.07671300081766148</v>
       </c>
       <c r="J2">
-        <v>0.03432112094178351</v>
+        <v>0.06483208570024364</v>
       </c>
       <c r="K2">
-        <v>2.234</v>
+        <v>4.214</v>
       </c>
       <c r="L2">
-        <v>0.05052012663952962</v>
+        <v>0.06891251022076861</v>
       </c>
       <c r="M2">
-        <v>1.3</v>
+        <v>1.655</v>
       </c>
       <c r="N2">
-        <v>0.02849002849002849</v>
+        <v>0.03791523482245132</v>
       </c>
       <c r="O2">
-        <v>0.5819158460161146</v>
+        <v>0.3927384907451352</v>
       </c>
       <c r="P2">
-        <v>1.3</v>
+        <v>1.655</v>
       </c>
       <c r="Q2">
-        <v>0.02849002849002849</v>
+        <v>0.03791523482245132</v>
       </c>
       <c r="R2">
-        <v>0.5819158460161146</v>
+        <v>0.3927384907451352</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>15.93</v>
+        <v>18.95</v>
       </c>
       <c r="V2">
-        <v>0.3491124260355029</v>
+        <v>0.434135166093929</v>
       </c>
       <c r="W2">
-        <v>0.08638743455497383</v>
+        <v>0.08029925187032419</v>
       </c>
       <c r="X2">
-        <v>0.146110285184423</v>
+        <v>0.1134901336571362</v>
       </c>
       <c r="Y2">
-        <v>-0.05972285062944915</v>
+        <v>-0.03319088178681205</v>
       </c>
       <c r="Z2">
-        <v>2.309138381201044</v>
+        <v>4.095505994240171</v>
       </c>
       <c r="AA2">
-        <v>0.07100428918110503</v>
+        <v>0.2694789652950382</v>
       </c>
       <c r="AB2">
-        <v>0.1457252115223188</v>
+        <v>0.1129125286028868</v>
       </c>
       <c r="AC2">
-        <v>-0.07463089690735815</v>
+        <v>0.1560676665161139</v>
       </c>
       <c r="AD2">
-        <v>0.608</v>
+        <v>1.588</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.608</v>
+        <v>1.588</v>
       </c>
       <c r="AG2">
-        <v>-15.322</v>
+        <v>-17.362</v>
       </c>
       <c r="AH2">
-        <v>0.01314935767117955</v>
+        <v>0.03510323179627747</v>
       </c>
       <c r="AI2">
-        <v>0.01869158878504673</v>
+        <v>0.04371283858181017</v>
       </c>
       <c r="AJ2">
-        <v>-0.5055430909330869</v>
+        <v>-0.6604534388314059</v>
       </c>
       <c r="AK2">
-        <v>-0.923123267863598</v>
+        <v>-0.9990792956611805</v>
       </c>
       <c r="AL2">
-        <v>0.019</v>
+        <v>0.032</v>
       </c>
       <c r="AM2">
-        <v>0.019</v>
+        <v>0.032</v>
       </c>
       <c r="AN2">
-        <v>0.247557003257329</v>
+        <v>0.293747687754347</v>
       </c>
       <c r="AO2">
-        <v>116.6842105263158</v>
+        <v>146.59375</v>
       </c>
       <c r="AP2">
-        <v>-6.238599348534201</v>
+        <v>-3.211616722160562</v>
       </c>
       <c r="AQ2">
-        <v>116.6842105263158</v>
+        <v>146.59375</v>
       </c>
     </row>
     <row r="3">
@@ -722,25 +722,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.136</v>
+        <v>0.108</v>
       </c>
       <c r="G3">
-        <v>0.1092592592592593</v>
+        <v>0.03695035460992908</v>
       </c>
       <c r="H3">
-        <v>0.1092592592592593</v>
+        <v>0.03695035460992908</v>
       </c>
       <c r="I3">
-        <v>0.1240740740740741</v>
+        <v>0.03978723404255319</v>
       </c>
       <c r="J3">
-        <v>0.08416720814381633</v>
+        <v>0.02888753799392097</v>
       </c>
       <c r="K3">
-        <v>1.16</v>
+        <v>0.432</v>
       </c>
       <c r="L3">
-        <v>0.1074074074074074</v>
+        <v>0.03063829787234043</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,46 +764,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.53</v>
+        <v>10.2</v>
       </c>
       <c r="V3">
-        <v>0.6172131147540985</v>
+        <v>1.260815822002472</v>
       </c>
       <c r="W3">
-        <v>0.1792890262751159</v>
+        <v>0.06162624821683309</v>
       </c>
       <c r="X3">
-        <v>0.146110285184423</v>
+        <v>0.1134901336571362</v>
       </c>
       <c r="Y3">
-        <v>0.03317874109069294</v>
+        <v>-0.05186388544030315</v>
       </c>
       <c r="AB3">
-        <v>0.1457252115223188</v>
+        <v>0.1129125286028868</v>
       </c>
       <c r="AD3">
-        <v>0.08699999999999999</v>
+        <v>0.123</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.08699999999999999</v>
+        <v>0.123</v>
       </c>
       <c r="AG3">
-        <v>-7.443000000000001</v>
+        <v>-10.077</v>
       </c>
       <c r="AH3">
-        <v>0.00708065435012615</v>
+        <v>0.01497625715329356</v>
       </c>
       <c r="AI3">
-        <v>0.01225870085951811</v>
+        <v>0.01439775254594405</v>
       </c>
       <c r="AJ3">
-        <v>-1.564641580828254</v>
+        <v>5.071464519375944</v>
       </c>
       <c r="AK3">
-        <v>17.18937644341799</v>
+        <v>6.081472540736271</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -812,10 +812,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.06214285714285715</v>
+        <v>0.1673469387755102</v>
       </c>
       <c r="AP3">
-        <v>-5.316428571428572</v>
+        <v>-13.71020408163265</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IronRock Insurance Company Limited (JMSE:ROC)</t>
+          <t>General Accident Insurance Company Jamaica Limited (JMSE:GENAC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,115 +835,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.308</v>
+        <v>0.194</v>
+      </c>
+      <c r="E4">
+        <v>0.133</v>
       </c>
       <c r="G4">
-        <v>0.09143835616438357</v>
+        <v>0.1094562647754137</v>
       </c>
       <c r="H4">
-        <v>0.09143835616438357</v>
+        <v>0.1094562647754137</v>
       </c>
       <c r="I4">
-        <v>0.1044520547945205</v>
+        <v>0.09007092198581561</v>
       </c>
       <c r="J4">
-        <v>0.09143018058936811</v>
+        <v>0.07689387969529814</v>
       </c>
       <c r="K4">
-        <v>0.33</v>
+        <v>3.46</v>
       </c>
       <c r="L4">
-        <v>0.113013698630137</v>
+        <v>0.08179669030732861</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>1.61</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.05015576323987539</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.4653179190751445</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>1.61</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.05015576323987539</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.4653179190751445</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>1.16</v>
+        <v>5.39</v>
       </c>
       <c r="V4">
-        <v>0.3483483483483483</v>
+        <v>0.1679127725856698</v>
       </c>
       <c r="W4">
-        <v>0.08638743455497383</v>
+        <v>0.1840425531914893</v>
       </c>
       <c r="X4">
-        <v>0.1458038488240062</v>
+        <v>0.1151499082436987</v>
       </c>
       <c r="Y4">
-        <v>-0.05941641426903241</v>
+        <v>0.06889264494779061</v>
       </c>
       <c r="Z4">
-        <v>0.7765957446808511</v>
+        <v>3.504556752278375</v>
       </c>
       <c r="AA4">
-        <v>0.07100428918110503</v>
+        <v>0.2694789652950382</v>
       </c>
       <c r="AB4">
-        <v>0.1456351860884632</v>
+        <v>0.1134112987789242</v>
       </c>
       <c r="AC4">
-        <v>-0.07463089690735815</v>
+        <v>0.1560676665161139</v>
       </c>
       <c r="AD4">
-        <v>0.011</v>
+        <v>1.45</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.011</v>
+        <v>1.45</v>
       </c>
       <c r="AG4">
-        <v>-1.149</v>
+        <v>-3.94</v>
       </c>
       <c r="AH4">
-        <v>0.003292427416941035</v>
+        <v>0.04321907600596125</v>
       </c>
       <c r="AI4">
-        <v>0.002735637901019647</v>
+        <v>0.0613107822410148</v>
       </c>
       <c r="AJ4">
-        <v>-0.5268225584594223</v>
+        <v>-0.1399147727272727</v>
       </c>
       <c r="AK4">
-        <v>-0.4016078294302692</v>
+        <v>-0.2157721796276013</v>
       </c>
       <c r="AL4">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="AM4">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="AN4">
-        <v>0.03206997084548104</v>
+        <v>0.3356481481481481</v>
       </c>
       <c r="AO4">
-        <v>25.41666666666666</v>
+        <v>238.125</v>
       </c>
       <c r="AP4">
-        <v>-3.349854227405248</v>
+        <v>-0.9120370370370369</v>
       </c>
       <c r="AQ4">
-        <v>25.41666666666666</v>
+        <v>238.125</v>
       </c>
     </row>
     <row r="5">
@@ -954,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Accident Insurance Company Jamaica Limited (JMSE:GENAC)</t>
+          <t>IronRock Insurance Company Limited (JMSE:ROC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,46 +969,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.21</v>
+        <v>0.221</v>
       </c>
       <c r="E5">
-        <v>-0.0582</v>
+        <v>0.585</v>
       </c>
       <c r="G5">
-        <v>0.0439344262295082</v>
+        <v>0.04652631578947369</v>
       </c>
       <c r="H5">
-        <v>0.0439344262295082</v>
+        <v>0.04652631578947369</v>
       </c>
       <c r="I5">
-        <v>0.01875409836065573</v>
+        <v>0.06736842105263158</v>
       </c>
       <c r="J5">
-        <v>0.009377049180327867</v>
+        <v>0.06437869822485207</v>
       </c>
       <c r="K5">
-        <v>0.744</v>
+        <v>0.322</v>
       </c>
       <c r="L5">
-        <v>0.02439344262295082</v>
+        <v>0.06778947368421052</v>
       </c>
       <c r="M5">
-        <v>1.3</v>
+        <v>0.045</v>
       </c>
       <c r="N5">
-        <v>0.04318936877076412</v>
+        <v>0.01300578034682081</v>
       </c>
       <c r="O5">
-        <v>1.747311827956989</v>
+        <v>0.139751552795031</v>
       </c>
       <c r="P5">
-        <v>1.3</v>
+        <v>0.045</v>
       </c>
       <c r="Q5">
-        <v>0.04318936877076412</v>
+        <v>0.01300578034682081</v>
       </c>
       <c r="R5">
-        <v>1.747311827956989</v>
+        <v>0.139751552795031</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,73 +1017,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>7.24</v>
+        <v>3.36</v>
       </c>
       <c r="V5">
-        <v>0.240531561461794</v>
+        <v>0.9710982658959537</v>
       </c>
       <c r="W5">
-        <v>0.03559808612440191</v>
+        <v>0.08029925187032419</v>
       </c>
       <c r="X5">
-        <v>0.1468958104057642</v>
+        <v>0.1128881597126952</v>
       </c>
       <c r="Y5">
-        <v>-0.1112977242813623</v>
+        <v>-0.03258890784237102</v>
       </c>
       <c r="Z5">
-        <v>1.98180636777128</v>
+        <v>1.660258650821391</v>
       </c>
       <c r="AA5">
-        <v>0.01858349577647823</v>
+        <v>0.1068852906564304</v>
       </c>
       <c r="AB5">
-        <v>0.1458804016677022</v>
+        <v>0.112732918011857</v>
       </c>
       <c r="AC5">
-        <v>-0.127296905891224</v>
+        <v>-0.005847627355426599</v>
       </c>
       <c r="AD5">
-        <v>0.51</v>
+        <v>0.015</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.51</v>
+        <v>0.015</v>
       </c>
       <c r="AG5">
-        <v>-6.73</v>
+        <v>-3.345</v>
       </c>
       <c r="AH5">
-        <v>0.01666122182293368</v>
+        <v>0.004316546762589928</v>
       </c>
       <c r="AI5">
-        <v>0.02382064455861747</v>
+        <v>0.003627569528415961</v>
       </c>
       <c r="AJ5">
-        <v>-0.2879760376551134</v>
+        <v>-29.08695652173908</v>
       </c>
       <c r="AK5">
-        <v>-0.4749470712773466</v>
+        <v>-4.316129032258062</v>
       </c>
       <c r="AL5">
-        <v>0.007</v>
+        <v>0.016</v>
       </c>
       <c r="AM5">
-        <v>0.007</v>
+        <v>0.016</v>
       </c>
       <c r="AN5">
-        <v>0.7152875175315568</v>
+        <v>0.04273504273504274</v>
       </c>
       <c r="AO5">
-        <v>81.71428571428571</v>
+        <v>20</v>
       </c>
       <c r="AP5">
-        <v>-9.438990182328192</v>
+        <v>-9.52991452991453</v>
       </c>
       <c r="AQ5">
-        <v>81.71428571428571</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
